--- a/TabletopWargameProject/V2/баланс модулей v2.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей v2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="116">
   <si>
     <t xml:space="preserve">Название орудия</t>
   </si>
@@ -187,13 +187,22 @@
     <t xml:space="preserve">Броня F/B/L/R</t>
   </si>
   <si>
-    <t xml:space="preserve">Полярность слота орудия</t>
+    <t xml:space="preserve">Полярности слота орудия</t>
   </si>
   <si>
     <t xml:space="preserve">Размер слота орудия</t>
   </si>
   <si>
     <t xml:space="preserve">MNT-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/2/2/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/4/4/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">α</t>
   </si>
   <si>
     <t xml:space="preserve">Название снаряда</t>
@@ -480,7 +489,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -498,10 +507,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1011,47 +1016,64 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="14.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.44"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="3" customFormat="true" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1073,39 +1095,39 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="39.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>62</v>
+      <c r="C2" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>3</v>
@@ -1116,13 +1138,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>5</v>
@@ -1130,13 +1152,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>62</v>
+      <c r="C4" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>3</v>
@@ -1144,13 +1166,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>68</v>
+      <c r="C5" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>3</v>
@@ -1158,13 +1180,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>68</v>
+      <c r="C6" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>3</v>
@@ -1172,13 +1194,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>68</v>
+      <c r="C7" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>3</v>
@@ -1191,8 +1213,8 @@
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>68</v>
+      <c r="C8" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>3</v>
@@ -1202,7 +1224,7 @@
     <row r="13" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H15" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>38</v>
@@ -1210,100 +1232,100 @@
     </row>
     <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="71.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H18" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H19" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="58.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H20" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H21" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H23" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H24" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H25" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H26" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H27" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H28" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1349,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14.6"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="14.52"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="3" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="52.24"/>
@@ -1336,72 +1358,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>100</v>
+      <c r="C2" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>103</v>
+      <c r="C3" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>106</v>
+      <c r="C4" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>38</v>
@@ -1409,26 +1431,26 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G8" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G9" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G10" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
